--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
+        <v>שמעון בוסקילה – עולם יפה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9e%d7%99%d7%a8-%d7%91%d7%a0%d7%99%d7%95%d7%9f-%d7%94%d7%99%d7%9b%d7%9f-%d7%90%d7%aa%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a2%d7%95%d7%9c%d7%9d-%d7%99%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הדואט בין שלומי שבת לבין עמיר בניון בנוי כמסע רוחני־קיומי: מצד אחד וידוי אישי, שבור ואינטימי. מצד שני זעקה גדולה שמופנית כלפי מעלה, אל האל או אל העצמי האבוד. הפתיחה ("הייתי קם עוזב הכול") נשמעת כמו הצהרת בריחה. הדובר מוכן</v>
+        <v>"עולם יפה" של שמעון בוסקילה מצליח לחבר בין כאב קולקטיבי לבין פופ נגיש מאוד. לכאורה מדובר בשיר פשוט למדי, אבל הפשטות היא חלק מרכזי מהאפקט שלו. השיר בנוי על שני צירים מנוגדים: כאב, געגוע ושבר, ומנגד תקווה, התמדה ובחירה בחיים.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
+        <v>שמעון בוסקילה – עולם יפה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%a9%d7%a8%d7%94-%d7%90%d7%aa-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f-%d7%a9%d7%9c-%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>שיאה של עונת החתונות בפתח. זה הזמן לקדם ללב הפלייליסט של שירי החתונה  את "לב לבן" של שולי רנד. את היוזמה ה"מסחרית" הזו לקחה לידיה מירי מסיקה בגרסה לשיר בעיבוד אורי זך. השיר "לב לבן" של  הפך תוך חודשים ספורים</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה – עולם יפה</v>
+        <v>משינה – כמעט וכאילו</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a2%d7%95%d7%9c%d7%9d-%d7%99%d7%a4%d7%94/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99%d7%a0%d7%94-%d7%9b%d7%9e%d7%a2%d7%98-%d7%95%d7%9b%d7%90%d7%99%d7%9c%d7%95/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"עולם יפה" של שמעון בוסקילה מצליח לחבר בין כאב קולקטיבי לבין פופ נגיש מאוד. לכאורה מדובר בשיר פשוט למדי, אבל הפשטות היא חלק מרכזי מהאפקט שלו. השיר בנוי על שני צירים מנוגדים: כאב, געגוע ושבר, ומנגד תקווה, התמדה ובחירה בחיים.</v>
+        <v>"כמעט כאילו" של משינה  מגיע אחרי יותר מארבעה עשורים של יצירה. במקום להציג הצהרה חגיגית או נוסטלגית על 40 שנות קריירה, משינה בוחרת לכתוב שיר על בלבול, ספק, מציאות מתעתעת וחוסר יכולת להכריע. במובן הזה, הוא נשמע מאוד עכשווי למרות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה – עולם יפה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%a9%d7%a8%d7%94-%d7%90%d7%aa-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f-%d7%a9%d7%9c-%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>שיאה של עונת החתונות בפתח. זה הזמן לקדם ללב הפלייליסט של שירי החתונה  את "לב לבן" של שולי רנד. את היוזמה ה"מסחרית" הזו לקחה לידיה מירי מסיקה בגרסה לשיר בעיבוד אורי זך. השיר "לב לבן" של  הפך תוך חודשים ספורים</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
+        <v>משינה – כמעט וכאילו</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משינה – כמעט וכאילו</v>
+        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99%d7%a0%d7%94-%d7%9b%d7%9e%d7%a2%d7%98-%d7%95%d7%9b%d7%90%d7%99%d7%9c%d7%95/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%a2%d7%93-%d7%9e%d7%90%d7%99%d7%a8-%d7%95%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%99%d7%95%d7%a6%d7%90%d7%aa-%d7%9e%d7%9f-%d7%94%d7%9b%d7%9c%d7%9c/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"כמעט כאילו" של משינה  מגיע אחרי יותר מארבעה עשורים של יצירה. במקום להציג הצהרה חגיגית או נוסטלגית על 40 שנות קריירה, משינה בוחרת לכתוב שיר על בלבול, ספק, מציאות מתעתעת וחוסר יכולת להכריע. במובן הזה, הוא נשמע מאוד עכשווי למרות</v>
+        <v>"יוצאת מן הכלל" של ליעד מאיר ואופק אדנק הוא שיר שממוקם היטב בתוך גל הפופ-הים תיכוני הצעיר של השנים האחרונות, כזה שמשלב דאנסהול, רגאטון, ראפ ופופ רומנטי קליל. הוא לא מנסה להיות שיר עמוק או מורכב במיוחד; המטרה שלו היא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משינה – כמעט וכאילו</v>
+        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>"וויסקי" ששר אור עמרמי ברוקמן, ממחיש את אחד מסימני ההיכר של שמוליק נויפלד כמלחין: היכולת לקחת טקסט פשוט יחסית, יומיומי כמעט, ולהעניק לו ממד רגשי רחב באמצעות לחן שנע בין עצב לתקווה. במסגרת הפרויקט "המשקפיים של שמוליק נויפלד". הטקסט מתאר</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%99%d7%93%d7%99%d7%93%d7%99%d7%94-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%a8%d7%91-%d7%97%d7%a6%d7%95%d7%99/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>"ערב חצוי" הוא אחד מאותם שירים שלא מבקשים לספר סיפור אלא ליצור מצב תודעתי. הוא פועל פחות כמו שיר עלילה ויותר כמו חלום עירוני, רצף של תמונות, חזיונות ואסוציאציות. הבחירה של רוני ידידיה להלחין דווקא טקסט של תרצה אתר אחרי</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
+        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%99%d7%a2%d7%93-%d7%9e%d7%90%d7%99%d7%a8-%d7%95%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%99%d7%95%d7%a6%d7%90%d7%aa-%d7%9e%d7%9f-%d7%94%d7%9b%d7%9c%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%90%d7%99%d7%a0%d7%98%d7%99%d7%9e%d7%99%d7%95%d7%aa-%d7%91%d7%96%d7%9e%d7%9f-%d7%9b%d7%90%d7%95%d7%98%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"יוצאת מן הכלל" של ליעד מאיר ואופק אדנק הוא שיר שממוקם היטב בתוך גל הפופ-הים תיכוני הצעיר של השנים האחרונות, כזה שמשלב דאנסהול, רגאטון, ראפ ופופ רומנטי קליל. הוא לא מנסה להיות שיר עמוק או מורכב במיוחד; המטרה שלו היא</v>
+        <v>"אינטימיות בזמן כאוטי" של בן ארצי מדבר על חרדה, בלבול ורעש חיצוני, אבל נשמע כמעט מנחם. הפער הזה בין התוכן לבין המעטפת המוזיקלית הוא כנראה אחד ממקורות הכוח שלו. השיר אינו עוסק באהבה רומנטית דווקא.  "אינטימיות" כאן היא כמעט צורך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>"וויסקי" ששר אור עמרמי ברוקמן, ממחיש את אחד מסימני ההיכר של שמוליק נויפלד כמלחין: היכולת לקחת טקסט פשוט יחסית, יומיומי כמעט, ולהעניק לו ממד רגשי רחב באמצעות לחן שנע בין עצב לתקווה. במסגרת הפרויקט "המשקפיים של שמוליק נויפלד". הטקסט מתאר</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%99%d7%93%d7%99%d7%93%d7%99%d7%94-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%a8%d7%91-%d7%97%d7%a6%d7%95%d7%99/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>"ערב חצוי" הוא אחד מאותם שירים שלא מבקשים לספר סיפור אלא ליצור מצב תודעתי. הוא פועל פחות כמו שיר עלילה ויותר כמו חלום עירוני, רצף של תמונות, חזיונות ואסוציאציות. הבחירה של רוני ידידיה להלחין דווקא טקסט של תרצה אתר אחרי</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
+        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
+        <v>פרויקט אסי עזר – כל מה שעוזר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%90%d7%99%d7%a0%d7%98%d7%99%d7%9e%d7%99%d7%95%d7%aa-%d7%91%d7%96%d7%9e%d7%9f-%d7%9b%d7%90%d7%95%d7%98%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%90%d7%a1%d7%99-%d7%a2%d7%96%d7%a8-%d7%9b%d7%9c-%d7%9e%d7%94-%d7%a9%d7%a2%d7%95%d7%96%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"אינטימיות בזמן כאוטי" של בן ארצי מדבר על חרדה, בלבול ורעש חיצוני, אבל נשמע כמעט מנחם. הפער הזה בין התוכן לבין המעטפת המוזיקלית הוא כנראה אחד ממקורות הכוח שלו. השיר אינו עוסק באהבה רומנטית דווקא.  "אינטימיות" כאן היא כמעט צורך</v>
+        <v>פרויקט "כל מה שעוזר" של אסי עזר, בשיתוף אבי אוחיון ומתן דרור, הוא דוגמה מעניינת לאופן שבו תרבות פופולרית יכולה לשמש כלי חברתי, חינוכי ורגשי גם יחד. מדובר לא רק בפרויקט מוזיקלי, אלא במיזם אודיו־ויזואלי בעל מטרה מוצהרת: להפוך את</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
+        <v>פרויקט אסי עזר – כל מה שעוזר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרויקט אסי עזר – כל מה שעוזר</v>
+        <v>דיסקו שמש – ימינושמאל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%90%d7%a1%d7%99-%d7%a2%d7%96%d7%a8-%d7%9b%d7%9c-%d7%9e%d7%94-%d7%a9%d7%a2%d7%95%d7%96%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%a1%d7%a7%d7%95-%d7%a9%d7%9e%d7%a9-%d7%99%d7%9e%d7%99%d7%a0%d7%95%d7%a9%d7%9e%d7%90%d7%9c/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>פרויקט "כל מה שעוזר" של אסי עזר, בשיתוף אבי אוחיון ומתן דרור, הוא דוגמה מעניינת לאופן שבו תרבות פופולרית יכולה לשמש כלי חברתי, חינוכי ורגשי גם יחד. מדובר לא רק בפרויקט מוזיקלי, אלא במיזם אודיו־ויזואלי בעל מטרה מוצהרת: להפוך את</v>
+        <v>השיר "ימינושמאל" של ההרכב "דיסקו שמש" (בשיתוף שי להב וצביקה כהן) מבצע פעולה מרתקת של פירוק והרכבה מחדש (דה-קונסטרוקציה) לקלאסיקה הציונית "אורחה במדבר" (יעקב פיכמן / דוד זהבי). בעוד השיר המקורי, המוכר בין היתר בביצועה המלנכולי-רומנטי של אסתר עופרים, מתאר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרויקט אסי עזר – כל מה שעוזר</v>
+        <v>דיסקו שמש – ימינושמאל</v>
       </c>
     </row>
   </sheetData>
